--- a/output/pdf_financials_xlsx/ARE.xlsx
+++ b/output/pdf_financials_xlsx/ARE.xlsx
@@ -1127,7 +1127,7 @@
         <v>17.089</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-9.279</v>
+        <v>-40.369</v>
       </c>
     </row>
     <row r="18">
@@ -1298,13 +1298,13 @@
         <v>30.381</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>161.89</v>
+        <v>-161.89</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-59.44</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>15.545</v>
+        <v>-15.545</v>
       </c>
     </row>
     <row r="21">
@@ -1427,13 +1427,13 @@
         <v>30.381</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>161.89</v>
+        <v>-161.89</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-59.44</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>15.545</v>
+        <v>-15.545</v>
       </c>
     </row>
     <row r="24">
@@ -1556,13 +1556,13 @@
         <v>64.64042600000001</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>77.090476</v>
+        <v>-77.090476</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>62.568421</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>67.586957</v>
+        <v>-67.586957</v>
       </c>
     </row>
     <row r="27">
@@ -1777,7 +1777,7 @@
         <v>-22.33009708737864</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>37.37914921044151</v>
+        <v>162.6208507895585</v>
       </c>
     </row>
     <row r="32">
@@ -1814,13 +1814,13 @@
         <v>0.6468928658880644</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>3.486122051525439</v>
+        <v>-3.486122051525439</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>-1.400984413105615</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>0.2860335055729152</v>
+        <v>-0.2860335055729152</v>
       </c>
     </row>
     <row r="33">
@@ -4647,13 +4647,13 @@
         <v>30.381</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>161.89</v>
+        <v>-161.89</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-59.44</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>15.545</v>
+        <v>-15.545</v>
       </c>
     </row>
     <row r="100">
@@ -26219,13 +26219,13 @@
         </is>
       </c>
       <c r="N281" s="5" t="n">
-        <v>161.89</v>
+        <v>-161.89</v>
       </c>
       <c r="O281" s="5" t="n">
         <v>-59.44</v>
       </c>
       <c r="P281" s="5" t="n">
-        <v>15.545</v>
+        <v>-15.545</v>
       </c>
     </row>
     <row r="282">

--- a/output/pdf_financials_xlsx/ARE.xlsx
+++ b/output/pdf_financials_xlsx/ARE.xlsx
@@ -1124,10 +1124,10 @@
         <v>15.655</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>17.089</v>
+        <v>-17.089</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-40.369</v>
+        <v>9.279</v>
       </c>
     </row>
     <row r="18">
@@ -1777,7 +1777,7 @@
         <v>-22.33009708737864</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>162.6208507895585</v>
+        <v>37.37914921044151</v>
       </c>
     </row>
     <row r="32">
@@ -26094,7 +26094,11 @@
           <t>Income tax recovery (expense) 20</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -27202,7 +27206,11 @@
           <t>Income tax recovery (expense) 21</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
